--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N39_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0002T0006Z000C1N39_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.38495638093895</v>
+        <v>4.450055411902579</v>
       </c>
       <c r="D2" t="n">
-        <v>6.108821850310852</v>
+        <v>0.9926835506755135</v>
       </c>
       <c r="E2" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F2" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.377089436838204</v>
+        <v>0.5487770334862081</v>
       </c>
       <c r="D3" t="n">
-        <v>17.55544016608683</v>
+        <v>2.85275902698911</v>
       </c>
       <c r="E3" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F3" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.07336338096693</v>
+        <v>7.811921549407127</v>
       </c>
       <c r="D4" t="n">
-        <v>45.3711417661431</v>
+        <v>7.372810536998253</v>
       </c>
       <c r="E4" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F4" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.15889004525373</v>
+        <v>4.738319632353732</v>
       </c>
       <c r="D5" t="n">
-        <v>26.4913548211072</v>
+        <v>4.30484515842992</v>
       </c>
       <c r="E5" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F5" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>2.474676612054906</v>
+        <v>0.4021349494589223</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7773288758765763</v>
+        <v>0.1263159423299436</v>
       </c>
       <c r="E6" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F6" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>19.63036670726056</v>
+        <v>3.189934589929841</v>
       </c>
       <c r="D7" t="n">
-        <v>19.00345679293243</v>
+        <v>3.08806172885152</v>
       </c>
       <c r="E7" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F7" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.13834496813212</v>
+        <v>3.75998105732147</v>
       </c>
       <c r="D8" t="n">
-        <v>26.05743330765731</v>
+        <v>4.234332912494313</v>
       </c>
       <c r="E8" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F8" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>44.22956786147197</v>
+        <v>7.187304777489196</v>
       </c>
       <c r="D9" t="n">
-        <v>39.23785379638208</v>
+        <v>6.376151241912089</v>
       </c>
       <c r="E9" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F9" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.77666839054092</v>
+        <v>6.626208613462899</v>
       </c>
       <c r="D10" t="n">
-        <v>40.25975365991382</v>
+        <v>6.542209969735996</v>
       </c>
       <c r="E10" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F10" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>60.83660695369359</v>
+        <v>9.885948629975209</v>
       </c>
       <c r="D11" t="n">
-        <v>50.21011947894844</v>
+        <v>8.159144415329122</v>
       </c>
       <c r="E11" t="n">
-        <v>17.95732650207522</v>
+        <v>2.918065556587223</v>
       </c>
       <c r="F11" t="n">
-        <v>15.74814570086478</v>
+        <v>2.559073676390526</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
